--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N86_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N86_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.48825279002045</v>
+        <v>9.504341078378323</v>
       </c>
       <c r="D2" t="n">
-        <v>21.47673159491453</v>
+        <v>3.489968884173611</v>
       </c>
       <c r="E2" t="n">
-        <v>15.93756299650088</v>
+        <v>2.589853986931393</v>
       </c>
       <c r="F2" t="n">
-        <v>12.85298560448492</v>
+        <v>2.0886101607288</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.98702406264706</v>
+        <v>6.010391410180147</v>
       </c>
       <c r="D3" t="n">
-        <v>39.24768671069808</v>
+        <v>6.377749090488438</v>
       </c>
       <c r="E3" t="n">
-        <v>15.93756299650088</v>
+        <v>2.589853986931393</v>
       </c>
       <c r="F3" t="n">
-        <v>12.85298560448492</v>
+        <v>2.0886101607288</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.59584747448089</v>
+        <v>1.721825214603145</v>
       </c>
       <c r="D4" t="n">
-        <v>13.22763132305118</v>
+        <v>2.149490089995816</v>
       </c>
       <c r="E4" t="n">
-        <v>15.93756299650088</v>
+        <v>2.589853986931393</v>
       </c>
       <c r="F4" t="n">
-        <v>12.85298560448492</v>
+        <v>2.0886101607288</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.95225089702379</v>
+        <v>4.379740770766366</v>
       </c>
       <c r="D5" t="n">
-        <v>28.84191296884336</v>
+        <v>4.686810857437047</v>
       </c>
       <c r="E5" t="n">
-        <v>15.93756299650088</v>
+        <v>2.589853986931393</v>
       </c>
       <c r="F5" t="n">
-        <v>12.85298560448492</v>
+        <v>2.0886101607288</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.77835620472209</v>
+        <v>6.13898288326734</v>
       </c>
       <c r="D6" t="n">
-        <v>37.24236393677941</v>
+        <v>6.051884139726655</v>
       </c>
       <c r="E6" t="n">
-        <v>15.93756299650088</v>
+        <v>2.589853986931393</v>
       </c>
       <c r="F6" t="n">
-        <v>12.85298560448492</v>
+        <v>2.0886101607288</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.78031114516727</v>
+        <v>8.251800561089683</v>
       </c>
       <c r="D7" t="n">
-        <v>36.68390840412822</v>
+        <v>5.961135115670835</v>
       </c>
       <c r="E7" t="n">
-        <v>15.93756299650088</v>
+        <v>2.589853986931393</v>
       </c>
       <c r="F7" t="n">
-        <v>12.85298560448492</v>
+        <v>2.0886101607288</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>54.74188958145105</v>
+        <v>8.895557056985798</v>
       </c>
       <c r="D8" t="n">
-        <v>2.235626241427224</v>
+        <v>0.363289264231924</v>
       </c>
       <c r="E8" t="n">
-        <v>15.93756299650088</v>
+        <v>2.589853986931393</v>
       </c>
       <c r="F8" t="n">
-        <v>12.85298560448492</v>
+        <v>2.0886101607288</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>63.73638564476759</v>
+        <v>10.35716266727473</v>
       </c>
       <c r="D9" t="n">
-        <v>9.636921028709333</v>
+        <v>1.565999667165267</v>
       </c>
       <c r="E9" t="n">
-        <v>15.93756299650088</v>
+        <v>2.589853986931393</v>
       </c>
       <c r="F9" t="n">
-        <v>12.85298560448492</v>
+        <v>2.0886101607288</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.10388152427203</v>
+        <v>5.704380747694206</v>
       </c>
       <c r="D10" t="n">
-        <v>33.83949509097893</v>
+        <v>5.498917952284076</v>
       </c>
       <c r="E10" t="n">
-        <v>15.93756299650088</v>
+        <v>2.589853986931393</v>
       </c>
       <c r="F10" t="n">
-        <v>12.85298560448492</v>
+        <v>2.0886101607288</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
